--- a/data/trans_dic/IP16A02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,07; 51,24</t>
+          <t>19,29; 53,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,93; 54,04</t>
+          <t>24,07; 54,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,36; 54,54</t>
+          <t>18,75; 54,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 54,42</t>
+          <t>5,39; 54,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,23; 64,62</t>
+          <t>28,44; 65,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,1; 56,15</t>
+          <t>22,36; 56,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,6; 67,69</t>
+          <t>21,24; 67,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,68; 65,39</t>
+          <t>23,27; 69,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,13; 53,3</t>
+          <t>27,39; 52,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,24; 50,27</t>
+          <t>26,94; 50,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,75; 55,4</t>
+          <t>24,86; 54,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,04; 52,78</t>
+          <t>18,51; 54,65</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,84; 42,05</t>
+          <t>24,73; 41,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,27; 52,64</t>
+          <t>36,48; 52,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,82; 45,44</t>
+          <t>30,7; 45,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,67; 52,81</t>
+          <t>16,87; 52,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,84; 45,49</t>
+          <t>28,1; 45,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,14; 49,03</t>
+          <t>35,14; 48,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,42; 41,88</t>
+          <t>25,57; 41,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,9; 48,76</t>
+          <t>33,04; 49,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,21; 40,85</t>
+          <t>28,82; 40,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38,41; 48,69</t>
+          <t>38,33; 48,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,75; 41,46</t>
+          <t>30,59; 41,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,43; 46,98</t>
+          <t>26,18; 46,66</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,23; 48,03</t>
+          <t>18,66; 51,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,39; 51,55</t>
+          <t>26,08; 50,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,64; 56,69</t>
+          <t>31,14; 57,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37,2; 61,98</t>
+          <t>36,94; 62,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,9; 64,27</t>
+          <t>35,88; 63,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,14; 46,36</t>
+          <t>20,15; 44,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,05; 56,67</t>
+          <t>31,6; 55,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,61; 66,33</t>
+          <t>38,3; 66,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,82; 53,54</t>
+          <t>32,33; 52,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,47; 42,52</t>
+          <t>26,67; 43,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,81; 52,07</t>
+          <t>34,28; 52,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,38; 60,28</t>
+          <t>42,42; 60,87</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,2; 40,04</t>
+          <t>25,9; 39,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,18; 47,32</t>
+          <t>36,17; 47,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,13; 45,07</t>
+          <t>32,81; 45,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,21; 50,31</t>
+          <t>24,32; 50,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,74; 48,05</t>
+          <t>34,76; 47,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,35; 45,05</t>
+          <t>33,53; 44,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,62; 44,17</t>
+          <t>30,69; 43,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,44; 50,87</t>
+          <t>37,46; 50,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,44; 41,49</t>
+          <t>32,63; 41,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,21; 44,92</t>
+          <t>36,28; 44,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,52; 42,23</t>
+          <t>33,53; 42,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,13; 48,3</t>
+          <t>32,5; 47,98</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7644</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9786</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6705</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3893</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9338</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8772</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5565</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6975</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>16981</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18558</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12270</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>10868</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4253; 11692</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6144; 14014</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3536; 10299</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>821; 8226</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5761; 13291</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5110; 12890</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2714; 8583</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3646; 10827</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>11588; 22388</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>13033; 24447</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7864; 17201</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5719; 16885</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>26353</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>51793</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39674</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>46876</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31968</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>52294</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>32587</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>48536</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>58320</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>104087</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>72261</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>95412</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>19962; 33140</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>42405; 60648</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>32512; 47887</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>20389; 63840</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>24633; 39856</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>43797; 61045</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>24786; 40059</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>39655; 58907</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>48523; 68935</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>92326; 117483</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>62048; 83863</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>63058; 112392</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7299</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17132</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16793</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>20748</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17311</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14132</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16000</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>24586</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>24610</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>31264</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>32794</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>45334</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4208; 11511</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11962; 22956</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11987; 22315</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15384; 26010</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>12653; 22494</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9116; 20025</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11899; 20846</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>17813; 30951</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>18693; 30508</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>24291; 39476</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>26102; 40223</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>37394; 53662</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>41295</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>78711</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>63172</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>71517</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58617</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75199</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>54153</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>80096</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>99912</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>153910</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>117324</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>151613</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>32457; 49838</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>67876; 89891</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>53571; 73725</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>43225; 89984</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>49774; 67965</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>64620; 86300</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>45230; 63813</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>68245; 92357</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>87606; 112185</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>138008; 171072</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>104160; 132584</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>116988; 172684</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,29; 53,03</t>
+          <t>19,77; 53,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,07; 54,91</t>
+          <t>23,81; 53,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,75; 54,62</t>
+          <t>20,12; 56,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 54,01</t>
+          <t>4,29; 52,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,44; 65,61</t>
+          <t>29,07; 65,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,36; 56,4</t>
+          <t>23,0; 55,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,24; 67,19</t>
+          <t>20,72; 66,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,27; 69,11</t>
+          <t>23,55; 66,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,39; 52,92</t>
+          <t>28,5; 53,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,94; 50,54</t>
+          <t>25,96; 49,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,86; 54,38</t>
+          <t>25,75; 54,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,51; 54,65</t>
+          <t>18,08; 53,51</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,73; 41,06</t>
+          <t>24,44; 41,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,48; 52,17</t>
+          <t>37,27; 52,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,7; 45,22</t>
+          <t>30,56; 45,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,87; 52,83</t>
+          <t>19,65; 52,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,1; 45,46</t>
+          <t>27,84; 44,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,14; 48,98</t>
+          <t>34,64; 49,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,57; 41,32</t>
+          <t>26,06; 41,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,04; 49,08</t>
+          <t>32,86; 48,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,82; 40,94</t>
+          <t>29,06; 40,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38,33; 48,77</t>
+          <t>37,93; 48,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,59; 41,34</t>
+          <t>30,33; 40,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,18; 46,66</t>
+          <t>26,64; 47,11</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,66; 51,05</t>
+          <t>18,8; 50,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,08; 50,06</t>
+          <t>26,21; 49,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,14; 57,97</t>
+          <t>30,97; 57,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,94; 62,46</t>
+          <t>37,39; 62,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,88; 63,78</t>
+          <t>35,7; 62,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,15; 44,27</t>
+          <t>19,87; 43,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,6; 55,36</t>
+          <t>30,26; 56,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,3; 66,55</t>
+          <t>38,18; 65,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,33; 52,77</t>
+          <t>32,51; 53,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,67; 43,34</t>
+          <t>26,88; 43,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,28; 52,82</t>
+          <t>33,69; 52,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42,42; 60,87</t>
+          <t>41,25; 60,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,9; 39,77</t>
+          <t>26,9; 40,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,17; 47,91</t>
+          <t>35,84; 48,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,81; 45,16</t>
+          <t>32,48; 44,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,32; 50,63</t>
+          <t>24,68; 50,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,76; 47,46</t>
+          <t>34,35; 47,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,53; 44,78</t>
+          <t>33,24; 45,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,69; 43,3</t>
+          <t>30,42; 43,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,46; 50,69</t>
+          <t>36,84; 50,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,63; 41,78</t>
+          <t>32,52; 42,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,28; 44,98</t>
+          <t>36,45; 45,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,53; 42,68</t>
+          <t>33,28; 42,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,5; 47,98</t>
+          <t>31,55; 47,77</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4253; 11692</t>
+          <t>4358; 11752</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6144; 14014</t>
+          <t>6077; 13705</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3536; 10299</t>
+          <t>3794; 10678</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>821; 8226</t>
+          <t>654; 7991</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5761; 13291</t>
+          <t>5890; 13171</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5110; 12890</t>
+          <t>5255; 12622</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2714; 8583</t>
+          <t>2647; 8491</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3646; 10827</t>
+          <t>3690; 10454</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11588; 22388</t>
+          <t>12058; 22522</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13033; 24447</t>
+          <t>12560; 23832</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7864; 17201</t>
+          <t>8144; 17201</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5719; 16885</t>
+          <t>5585; 16534</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19962; 33140</t>
+          <t>19726; 33144</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42405; 60648</t>
+          <t>43333; 60987</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32512; 47887</t>
+          <t>32361; 47772</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20389; 63840</t>
+          <t>23751; 63399</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24633; 39856</t>
+          <t>24405; 38735</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43797; 61045</t>
+          <t>43166; 61633</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24786; 40059</t>
+          <t>25267; 40433</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39655; 58907</t>
+          <t>39441; 58085</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48523; 68935</t>
+          <t>48938; 68169</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92326; 117483</t>
+          <t>91360; 116417</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62048; 83863</t>
+          <t>61524; 83031</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>63058; 112392</t>
+          <t>64157; 113482</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4208; 11511</t>
+          <t>4239; 11421</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11962; 22956</t>
+          <t>12021; 22774</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11987; 22315</t>
+          <t>11922; 21945</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15384; 26010</t>
+          <t>15572; 26154</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12653; 22494</t>
+          <t>12589; 21990</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9116; 20025</t>
+          <t>8987; 19799</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11899; 20846</t>
+          <t>11397; 21157</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17813; 30951</t>
+          <t>17756; 30629</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18693; 30508</t>
+          <t>18798; 31049</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24291; 39476</t>
+          <t>24481; 39195</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26102; 40223</t>
+          <t>25659; 40021</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37394; 53662</t>
+          <t>36359; 52893</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32457; 49838</t>
+          <t>33713; 51225</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67876; 89891</t>
+          <t>67251; 90680</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53571; 73725</t>
+          <t>53029; 73357</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43225; 89984</t>
+          <t>43856; 89860</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49774; 67965</t>
+          <t>49181; 67521</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64620; 86300</t>
+          <t>64064; 87054</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45230; 63813</t>
+          <t>44835; 63534</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68245; 92357</t>
+          <t>67131; 91778</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87606; 112185</t>
+          <t>87309; 113601</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>138008; 171072</t>
+          <t>138640; 172841</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>104160; 132584</t>
+          <t>103391; 131952</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>116988; 172684</t>
+          <t>113536; 171925</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Estudios-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>46,1%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38,39%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>43,56%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>48,97%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>34,67%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>38,34%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>35,56%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25,56%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46,1%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>38,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,56%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>44,14%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,77; 53,3</t>
+          <t>28,23; 64,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,81; 53,7</t>
+          <t>24,1; 56,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,12; 56,63</t>
+          <t>21,6; 67,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 52,47</t>
+          <t>24,29; 69,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,07; 65,02</t>
+          <t>19,07; 51,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,0; 55,23</t>
+          <t>21,93; 54,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,72; 66,46</t>
+          <t>20,36; 54,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,55; 66,72</t>
+          <t>16,31; 64,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,5; 53,24</t>
+          <t>29,13; 53,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,96; 49,26</t>
+          <t>27,24; 50,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,75; 54,38</t>
+          <t>25,75; 55,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,08; 53,51</t>
+          <t>27,62; 61,2</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>36,46%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>41,96%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>33,61%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>39,68%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>32,65%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>44,55%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>37,46%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>38,79%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,46%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>41,96%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>33,61%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,44; 41,07</t>
+          <t>28,84; 45,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,27; 52,46</t>
+          <t>35,14; 49,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,56; 45,11</t>
+          <t>26,42; 41,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,65; 52,46</t>
+          <t>31,93; 48,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,84; 44,18</t>
+          <t>25,84; 42,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,64; 49,46</t>
+          <t>37,27; 52,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,06; 41,7</t>
+          <t>30,82; 45,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,86; 48,39</t>
+          <t>41,03; 58,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,06; 40,49</t>
+          <t>29,21; 40,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,93; 48,33</t>
+          <t>38,41; 48,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,33; 40,93</t>
+          <t>30,75; 41,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,64; 47,11</t>
+          <t>38,56; 50,35</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>49,09%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>31,24%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>42,49%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>53,12%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>32,37%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>37,36%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>43,63%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>49,83%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>49,09%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>42,49%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,8; 50,64</t>
+          <t>35,9; 64,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,21; 49,66</t>
+          <t>21,14; 46,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,97; 57,01</t>
+          <t>30,05; 56,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37,39; 62,81</t>
+          <t>38,21; 66,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,7; 62,36</t>
+          <t>18,23; 48,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,87; 43,77</t>
+          <t>27,39; 51,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,26; 56,18</t>
+          <t>31,64; 56,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,18; 65,85</t>
+          <t>36,17; 60,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,51; 53,7</t>
+          <t>32,82; 53,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,88; 43,03</t>
+          <t>25,47; 42,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,69; 52,55</t>
+          <t>33,81; 52,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,25; 60,0</t>
+          <t>41,24; 59,92</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40,94%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39,02%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>36,74%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43,98%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>32,96%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>41,95%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>38,69%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>40,24%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40,94%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,74%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,9; 40,88</t>
+          <t>34,74; 48,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,84; 48,33</t>
+          <t>33,35; 45,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,48; 44,93</t>
+          <t>30,62; 44,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,68; 50,56</t>
+          <t>37,41; 51,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,35; 47,15</t>
+          <t>26,2; 40,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,24; 45,17</t>
+          <t>35,18; 47,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,42; 43,11</t>
+          <t>33,13; 45,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,84; 50,37</t>
+          <t>42,06; 55,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,52; 42,31</t>
+          <t>32,44; 41,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,45; 45,44</t>
+          <t>36,21; 44,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,28; 42,48</t>
+          <t>33,52; 42,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,55; 47,77</t>
+          <t>41,64; 50,97</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9338</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8772</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5565</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6816</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>7644</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>9786</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>6705</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3893</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9338</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8772</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5565</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>10463</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4358; 11752</t>
+          <t>5719; 13091</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6077; 13705</t>
+          <t>5508; 12832</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3794; 10678</t>
+          <t>2760; 8648</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>654; 7991</t>
+          <t>3381; 9635</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5890; 13171</t>
+          <t>4204; 11297</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5255; 12622</t>
+          <t>5597; 13793</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2647; 8491</t>
+          <t>3839; 10284</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3690; 10454</t>
+          <t>1595; 6333</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12058; 22522</t>
+          <t>12323; 22548</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12560; 23832</t>
+          <t>13178; 24319</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8144; 17201</t>
+          <t>8146; 17522</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5585; 16534</t>
+          <t>6547; 14506</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>74</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31968</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>52294</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32587</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42823</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>26353</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>39674</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>46876</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31968</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>52294</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>32587</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>48536</t>
+          <t>46137</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95412</t>
+          <t>88960</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19726; 33144</t>
+          <t>25280; 39878</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43333; 60987</t>
+          <t>43793; 61102</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32361; 47772</t>
+          <t>25611; 40601</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23751; 63399</t>
+          <t>34458; 52220</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24405; 38735</t>
+          <t>20857; 33938</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43166; 61633</t>
+          <t>43323; 61197</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25267; 40433</t>
+          <t>32645; 48125</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39441; 58085</t>
+          <t>38029; 53860</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48938; 68169</t>
+          <t>49180; 68779</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91360; 116417</t>
+          <t>92517; 117276</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61524; 83031</t>
+          <t>62376; 84116</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>64157; 113482</t>
+          <t>77344; 101003</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17311</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14132</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16000</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22903</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>7299</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>17132</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>16793</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20748</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>17311</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>14132</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>16000</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24586</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45334</t>
+          <t>42764</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4239; 11421</t>
+          <t>12661; 22665</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12021; 22774</t>
+          <t>9561; 20972</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11922; 21945</t>
+          <t>11317; 21340</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15572; 26154</t>
+          <t>16478; 28793</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12589; 21990</t>
+          <t>4110; 10831</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8987; 19799</t>
+          <t>12563; 23641</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11397; 21157</t>
+          <t>12180; 21823</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17756; 30629</t>
+          <t>14658; 24642</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18798; 31049</t>
+          <t>18975; 30957</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24481; 39195</t>
+          <t>23199; 38736</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25659; 40021</t>
+          <t>25749; 39650</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36359; 52893</t>
+          <t>34493; 50124</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>114</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>58617</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>75199</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>54153</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>72542</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>41295</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>78711</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>63172</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>71517</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>58617</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>75199</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>54153</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>80096</t>
+          <t>69644</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>151613</t>
+          <t>142186</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33713; 51225</t>
+          <t>49748; 68803</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67251; 90680</t>
+          <t>64263; 86818</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53029; 73357</t>
+          <t>45123; 65094</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43856; 89860</t>
+          <t>61711; 84667</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49181; 67521</t>
+          <t>32833; 50167</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64064; 87054</t>
+          <t>66003; 88793</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44835; 63534</t>
+          <t>54080; 73578</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>67131; 91778</t>
+          <t>60145; 80004</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87309; 113601</t>
+          <t>87112; 111390</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>138640; 172841</t>
+          <t>137731; 170864</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103391; 131952</t>
+          <t>104113; 131183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>113536; 171925</t>
+          <t>128241; 156954</t>
         </is>
       </c>
     </row>
